--- a/civic_led/impact4.xlsx
+++ b/civic_led/impact4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\civic_led\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4029C3F-00AB-4B72-B964-DE6E697270B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18329AA-2137-48FC-9BD1-A63A642B7370}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>Process</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>t/t of waste</t>
-  </si>
-  <si>
-    <t>Comp_IC</t>
   </si>
   <si>
     <t>AD-d</t>
@@ -274,16 +271,17 @@
       <sheetName val="LCI"/>
       <sheetName val="LCI_AD-d"/>
       <sheetName val="params_HC"/>
-      <sheetName val="LCI_HC"/>
       <sheetName val="LCI_AD-a"/>
       <sheetName val="LCI_AD-c"/>
+      <sheetName val="LCI_HC"/>
       <sheetName val="LCI_AD-b"/>
+      <sheetName val="LCIA_AD-b"/>
       <sheetName val="LCIA_HC"/>
-      <sheetName val="LCIA_AD-b"/>
       <sheetName val="LCIA_AD-c"/>
       <sheetName val="LCIA_AD-d"/>
       <sheetName val="LCIA_AD-e"/>
       <sheetName val="Figures"/>
+      <sheetName val="Figures_transport"/>
       <sheetName val="IW+f"/>
       <sheetName val="LCIA_AD-a"/>
       <sheetName val="LCIA_IC"/>
@@ -324,34 +322,40 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="42">
+          <cell r="E42">
+            <v>3876.4660709036466</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
       <sheetData sheetId="13">
+        <row r="99">
+          <cell r="AG99">
+            <v>-201.83380910205278</v>
+          </cell>
+          <cell r="AH99">
+            <v>-1.6840731926744631E-3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="14">
         <row r="46">
           <cell r="AG46">
             <v>-209.55449775755659</v>
           </cell>
           <cell r="AH46">
             <v>-2.4452708210737869E-3</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="14">
-        <row r="99">
-          <cell r="AG99">
-            <v>-201.83380910205278</v>
-          </cell>
-          <cell r="AH99">
-            <v>-1.6840731926744631E-3</v>
           </cell>
         </row>
       </sheetData>
@@ -385,9 +389,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
       <sheetData sheetId="20">
+        <row r="4">
+          <cell r="C4">
+            <v>0.189012950359117</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="21">
         <row r="81">
           <cell r="AG81">
             <v>-194.89855950499845</v>
@@ -397,7 +408,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21">
+      <sheetData sheetId="22">
         <row r="84">
           <cell r="AG84">
             <v>-140.00263317406106</v>
@@ -407,13 +418,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -657,13 +668,37 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="8">
+        <row r="24">
+          <cell r="E24">
+            <v>509.03089819946877</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="10">
+        <row r="24">
+          <cell r="E24">
+            <v>509.03089819946877</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="23">
+          <cell r="E23">
+            <v>131.83340888752835</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="14">
+        <row r="15">
+          <cell r="E15">
+            <v>11.6046876865655</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="15">
         <row r="75">
           <cell r="C75">
@@ -674,7 +709,13 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="19">
+        <row r="25">
+          <cell r="E25">
+            <v>9.1614439984537466</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="20">
         <row r="43">
           <cell r="C43">
@@ -991,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9A6E0B-B9EE-48A8-800F-BDEF0A29E888}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.1796875" customWidth="1"/>
@@ -1016,10 +1057,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1030,10 +1071,10 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s">
         <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1206,7 +1247,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1230,7 +1271,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1254,7 +1295,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1278,7 +1319,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1449,6 +1490,12 @@
         <f>'[3]IW+f'!$G$28</f>
         <v>2.3755902490883187</v>
       </c>
+      <c r="E23">
+        <v>1.2566999999999999</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.3917000000000001E-5</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
@@ -1465,6 +1512,12 @@
         <f>'[3]IW+f'!$G$30</f>
         <v>0.92484418441705429</v>
       </c>
+      <c r="E24">
+        <v>0.51358999999999999</v>
+      </c>
+      <c r="F24" s="3">
+        <v>5.1734999999999997E-6</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
@@ -1481,6 +1534,12 @@
         <f>'[3]IW+f'!$G$29</f>
         <v>0.31390973645585518</v>
       </c>
+      <c r="E25">
+        <v>0.72350000000000003</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5.6199000000000002E-6</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
@@ -1497,6 +1556,12 @@
         <f>'[3]IW+f'!$G$31</f>
         <v>3.2008550717339546E-2</v>
       </c>
+      <c r="E26">
+        <v>1.2982469999999999E-2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1.0766E-7</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -1513,6 +1578,12 @@
         <f>'[3]IW+f'!$G$39</f>
         <v>1.1130534401230463E-2</v>
       </c>
+      <c r="E27">
+        <v>6.9578360000000006E-2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>6.7176999999999999E-7</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
@@ -1529,6 +1600,12 @@
         <f>'[3]IW+f'!$G$37</f>
         <v>1.371409771705601E-2</v>
       </c>
+      <c r="E28">
+        <v>0.10004979</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4.3286000000000003E-7</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
@@ -1545,6 +1622,12 @@
         <f>'[3]IW+f'!$G$38</f>
         <v>7.8893246702014919E-2</v>
       </c>
+      <c r="E29">
+        <v>0.46230322000000001</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3.9848000000000004E-6</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
@@ -1565,10 +1648,16 @@
       <c r="D31">
         <v>0</v>
       </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
         <v>42</v>
@@ -1580,28 +1669,59 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
       <c r="D34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1609,13 +1729,19 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1623,18 +1749,10 @@
       <c r="D36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>0</v>
       </c>
     </row>
